--- a/files/CO02027.CLT02952.xlsx
+++ b/files/CO02027.CLT02952.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\node\excel-cli\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232E5EE4-1009-4B16-B7C7-77192873B253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1642B0-EABF-4564-A31C-24756A06F2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4C06D2D4-484F-4AF6-A64F-B122DA8DB842}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>Product Name</t>
   </si>
@@ -120,6 +120,27 @@
   </si>
   <si>
     <t>AMG-BFX-001-RG</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>TRY</t>
+  </si>
+  <si>
+    <t>AED</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -508,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72FA345-8F09-4AA4-A4DB-526F1813E9F0}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.6328125" customWidth="1"/>
@@ -517,7 +538,7 @@
     <col min="7" max="7" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,8 +560,11 @@
       <c r="G1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -562,8 +586,11 @@
       <c r="G2" s="3">
         <v>46411</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -585,8 +612,11 @@
       <c r="G3" s="3">
         <v>46412</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -608,8 +638,11 @@
       <c r="G4" s="3">
         <v>46413</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -631,8 +664,11 @@
       <c r="G5" s="3">
         <v>46414</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -654,8 +690,11 @@
       <c r="G6" s="3">
         <v>46415</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -677,8 +716,11 @@
       <c r="G7" s="3">
         <v>46416</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -700,8 +742,11 @@
       <c r="G8" s="3">
         <v>46417</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -723,8 +768,11 @@
       <c r="G9" s="3">
         <v>46418</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -746,8 +794,11 @@
       <c r="G10" s="3">
         <v>46419</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -768,6 +819,9 @@
       </c>
       <c r="G11" s="3">
         <v>46420</v>
+      </c>
+      <c r="H11" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
